--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_sk_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_sk_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>11-03-2021 08:30</t>
+          <t>2021-11-03 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>23-01-2021 08:30</t>
+          <t>2021-01-23 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>16-01-2021 08:30</t>
+          <t>2021-01-16 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
